--- a/templates/all_options_input_template.xlsx
+++ b/templates/all_options_input_template.xlsx
@@ -129,6 +129,226 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pittacia Insectorum</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with StateProv and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and StateProv; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 2 by itself. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with Verbatim_Date and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with elevation and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 5. Spaces after initials are removed for display. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with microhabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with macrohabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pittacia Insectorum</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with StateProv and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and StateProv; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 2 by itself. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with Verbatim_Date and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with elevation and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 5. Spaces after initials are removed for display. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with microhabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with macrohabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pittacia Insectorum</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with StateProv and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and StateProv; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 2 by itself. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with Verbatim_Date and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with elevation and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 5. Spaces after initials are removed for display. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with microhabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with macrohabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pittacia Insectorum</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with StateProv and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and County; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 1 with Country and StateProv; count punctuation/spaces too. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 2 by itself. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with Verbatim_Date and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 4 with elevation and a comma/space. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Uses line 5. Spaces after initials are removed for display. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with microhabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Normal-layout length guidance (not a restriction): Arial roughly 20–23 characters at 4 pt or 23–25 at 3.5 pt per full line, including spaces/punctuation. Width varies with letters. Shares line 6 with macrohabitat at 3.5 pt; may have less room near Field Number. Separate-habitat mode has different limits. See docs/text_length_guidance.md and check the generated PDF/report.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,7 +641,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -513,6 +733,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -523,7 +744,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -615,6 +836,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -625,7 +847,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -717,6 +939,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -727,7 +950,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -825,6 +1048,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -835,7 +1059,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
   </cols>
@@ -859,7 +1083,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -907,7 +1131,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
   </cols>
@@ -931,7 +1155,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>

--- a/templates/all_options_input_template.xlsx
+++ b/templates/all_options_input_template.xlsx
@@ -15,6 +15,8 @@
     <sheet name="Determination" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Pin_Barcode" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Instructions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Collection_Only" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Collection_Only_Paired" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -737,6 +739,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StateProvince</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>LocalityLabel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Verbatim_Elevation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Verbatim_Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Collector_Label</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>MacroHabitat_Label</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Microhabitat_Label</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Field_Number</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Sampling_Protocol</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1154,7 +1258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1257,6 +1361,126 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Collection_Only</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>--mode collection-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Collection_Only_Paired</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>--mode collection-only --separate-habitat --include-method</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StateProvince</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>LocalityLabel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Verbatim_Elevation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Verbatim_Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Collector_Label</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>MacroHabitat_Label</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Microhabitat_Label</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Field_Number</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/all_options_input_template.xlsx
+++ b/templates/all_options_input_template.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Instructions" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Collection_Only" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Collection_Only_Paired" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Collection_Only_Wrapped" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -841,6 +842,102 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StateProvince</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>LocalityLabel</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Verbatim_Elevation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Verbatim_Date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Collector_Label</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>MacroHabitat_Label</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Microhabitat_Label</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Field_Number</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1258,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1382,6 +1479,18 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>--mode collection-only --separate-habitat --include-method</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Collection_Only_Wrapped</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>--mode collection-only --layout flow</t>
         </is>
       </c>
     </row>
